--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -6137,7 +6137,7 @@
         <v>106870130</v>
       </c>
       <c r="B47" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -6152,11 +6152,6 @@
       <c r="E47" t="n">
         <v>103021</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -6137,7 +6137,7 @@
         <v>106870130</v>
       </c>
       <c r="B47" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6151,6 +6151,11 @@
       </c>
       <c r="E47" t="n">
         <v>103021</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -6137,7 +6137,7 @@
         <v>106870130</v>
       </c>
       <c r="B47" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12611,118 +12611,6 @@
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>114635966</v>
-      </c>
-      <c r="B101" t="n">
-        <v>94322</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Dicranum flagellare</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>A 58937, Näringe, Sm</t>
-        </is>
-      </c>
-      <c r="Q101" t="n">
-        <v>568123</v>
-      </c>
-      <c r="R101" t="n">
-        <v>6423376</v>
-      </c>
-      <c r="S101" t="n">
-        <v>25</v>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Odensvi</t>
-        </is>
-      </c>
-      <c r="Y101" t="inlineStr">
-        <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>2023-02-19</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På tuva i kärr.</t>
-        </is>
-      </c>
-      <c r="AD101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF101" t="inlineStr"/>
-      <c r="AG101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT101" t="inlineStr"/>
-      <c r="AW101" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12725,10 +12725,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124356754</v>
+        <v>124356741</v>
       </c>
       <c r="B102" t="n">
-        <v>78834</v>
+        <v>79428</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12737,25 +12737,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124356741</v>
+        <v>124356754</v>
       </c>
       <c r="B103" t="n">
-        <v>79428</v>
+        <v>78834</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12849,25 +12849,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12613,10 +12613,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124356861</v>
+        <v>124356754</v>
       </c>
       <c r="B101" t="n">
-        <v>78546</v>
+        <v>78834</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12625,25 +12625,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12725,10 +12725,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124356741</v>
+        <v>124356861</v>
       </c>
       <c r="B102" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12741,21 +12741,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124356754</v>
+        <v>124356741</v>
       </c>
       <c r="B103" t="n">
-        <v>78834</v>
+        <v>79428</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12849,25 +12849,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12725,10 +12725,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124356861</v>
+        <v>124356741</v>
       </c>
       <c r="B102" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12741,21 +12741,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124356741</v>
+        <v>124356861</v>
       </c>
       <c r="B103" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12853,21 +12853,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12613,10 +12613,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124356754</v>
+        <v>124356741</v>
       </c>
       <c r="B101" t="n">
-        <v>78834</v>
+        <v>79428</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12625,25 +12625,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12725,10 +12725,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124356741</v>
+        <v>124356861</v>
       </c>
       <c r="B102" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12741,21 +12741,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124356861</v>
+        <v>124356754</v>
       </c>
       <c r="B103" t="n">
-        <v>78546</v>
+        <v>78834</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12849,25 +12849,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12613,10 +12613,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124356741</v>
+        <v>124356861</v>
       </c>
       <c r="B101" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12629,21 +12629,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12725,10 +12725,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124356861</v>
+        <v>124356741</v>
       </c>
       <c r="B102" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12741,21 +12741,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD102" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12725,10 +12725,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124356741</v>
+        <v>124356754</v>
       </c>
       <c r="B102" t="n">
-        <v>79428</v>
+        <v>78834</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12737,25 +12737,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124356754</v>
+        <v>124356741</v>
       </c>
       <c r="B103" t="n">
-        <v>78834</v>
+        <v>79428</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12849,25 +12849,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12613,10 +12613,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124356861</v>
+        <v>124356741</v>
       </c>
       <c r="B101" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12629,21 +12629,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124356741</v>
+        <v>124356861</v>
       </c>
       <c r="B103" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12853,21 +12853,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12613,10 +12613,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124356741</v>
+        <v>124356754</v>
       </c>
       <c r="B101" t="n">
-        <v>79428</v>
+        <v>78834</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12625,25 +12625,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12725,10 +12725,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124356754</v>
+        <v>124356741</v>
       </c>
       <c r="B102" t="n">
-        <v>78834</v>
+        <v>79428</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12737,25 +12737,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD102" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12613,10 +12613,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124356754</v>
+        <v>124356741</v>
       </c>
       <c r="B101" t="n">
-        <v>78834</v>
+        <v>79428</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12625,25 +12625,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12725,10 +12725,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124356741</v>
+        <v>124356754</v>
       </c>
       <c r="B102" t="n">
-        <v>79428</v>
+        <v>78834</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12737,25 +12737,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD102" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12613,10 +12613,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124356741</v>
+        <v>124356861</v>
       </c>
       <c r="B101" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12629,21 +12629,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124356861</v>
+        <v>124356741</v>
       </c>
       <c r="B103" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12853,21 +12853,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12613,10 +12613,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124356861</v>
+        <v>124356754</v>
       </c>
       <c r="B101" t="n">
-        <v>78546</v>
+        <v>78834</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12625,25 +12625,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12725,10 +12725,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124356754</v>
+        <v>124356741</v>
       </c>
       <c r="B102" t="n">
-        <v>78834</v>
+        <v>79428</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12737,25 +12737,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124356741</v>
+        <v>124356861</v>
       </c>
       <c r="B103" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12853,21 +12853,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -12613,10 +12613,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124356754</v>
+        <v>124356861</v>
       </c>
       <c r="B101" t="n">
-        <v>78834</v>
+        <v>78546</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12625,25 +12625,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12837,10 +12837,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124356861</v>
+        <v>124356754</v>
       </c>
       <c r="B103" t="n">
-        <v>78546</v>
+        <v>78834</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12849,25 +12849,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 58937-2022 artfynd.xlsx
+++ b/artfynd/A 58937-2022 artfynd.xlsx
@@ -10883,7 +10883,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
